--- a/data/trans_orig/IQ23_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100268</t>
+          <t>101301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116001</t>
+          <t>115693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>110858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>127063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214210</t>
+          <t>215379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237780</t>
+          <t>237591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>40862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>50864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74245</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158605</t>
+          <t>158328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155016</t>
+          <t>154669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173812</t>
+          <t>173590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301099</t>
+          <t>301144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326880</t>
+          <t>328619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37644</t>
+          <t>37866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56440</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79085</t>
+          <t>77346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104866</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99193</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>98077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115384</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184988</t>
+          <t>185304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209370</t>
+          <t>210021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54737</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>51097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101093</t>
+          <t>100777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136057</t>
+          <t>135697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158934</t>
+          <t>158117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>130431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151546</t>
+          <t>151904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273582</t>
+          <t>274114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304756</t>
+          <t>303306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>48873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70933</t>
+          <t>71293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55583</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76879</t>
+          <t>76698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109363</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140537</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>159460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197674</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169431</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207720</t>
+          <t>205481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338766</t>
+          <t>339280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391552</t>
+          <t>391712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>98760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114949</t>
+          <t>115276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100081</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205414</t>
+          <t>205021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230137</t>
+          <t>228928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53935</t>
+          <t>53091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63236</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87959</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140940</t>
+          <t>140100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160478</t>
+          <t>159911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>147539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170170</t>
+          <t>169409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294006</t>
+          <t>295464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324979</t>
+          <t>324177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>46447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65418</t>
+          <t>66258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>53758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>75628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104546</t>
+          <t>105348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135519</t>
+          <t>134061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93102</t>
+          <t>94535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111779</t>
+          <t>112535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110847</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128872</t>
+          <t>128908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208620</t>
+          <t>208748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235496</t>
+          <t>234647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61599</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>56209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85797</t>
+          <t>86646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112673</t>
+          <t>112545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138767</t>
+          <t>138212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161735</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>136521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158768</t>
+          <t>158336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282248</t>
+          <t>282231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313317</t>
+          <t>312740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47778</t>
+          <t>48472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72060</t>
+          <t>71875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104592</t>
+          <t>105169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135661</t>
+          <t>135678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219761</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>194823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>235240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382470</t>
+          <t>384075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439625</t>
+          <t>442146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98767</t>
+          <t>98601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95360</t>
+          <t>96250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199603</t>
+          <t>198590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223634</t>
+          <t>222992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52716</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58149</t>
+          <t>58791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82180</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122487</t>
+          <t>121697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143366</t>
+          <t>143436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133166</t>
+          <t>132883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155742</t>
+          <t>155643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>260957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292574</t>
+          <t>293822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83660</t>
+          <t>84450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>90850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137306</t>
+          <t>136058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168983</t>
+          <t>168923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94199</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112177</t>
+          <t>110926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>98594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118113</t>
+          <t>118485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199020</t>
+          <t>197184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224784</t>
+          <t>225080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59193</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>65783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92985</t>
+          <t>92689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118749</t>
+          <t>120585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125559</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148532</t>
+          <t>148862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124876</t>
+          <t>123503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147211</t>
+          <t>146603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257479</t>
+          <t>258075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291108</t>
+          <t>289525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>57145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80448</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77180</t>
+          <t>78553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116955</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150584</t>
+          <t>149988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198807</t>
+          <t>201633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223042</t>
+          <t>222887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264160</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>438240</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>497617</t>
+          <t>491817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>87689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110076</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168640</t>
+          <t>168474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195003</t>
+          <t>195201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59007</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85370</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129021</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149491</t>
+          <t>149487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168742</t>
+          <t>168907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>194046</t>
+          <t>193958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>305051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>338525</t>
+          <t>337754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>41025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61491</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60989</t>
+          <t>61077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86293</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107023</t>
+          <t>107794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141211</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126145</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157739</t>
+          <t>158208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108534</t>
+          <t>108542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135289</t>
+          <t>134291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242609</t>
+          <t>243568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288096</t>
+          <t>289660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61647</t>
+          <t>62320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49601</t>
+          <t>50599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>76348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84586</t>
+          <t>83022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130073</t>
+          <t>129114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95883</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116596</t>
+          <t>116921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114529</t>
+          <t>114470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137207</t>
+          <t>135842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216535</t>
+          <t>217619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247676</t>
+          <t>247367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70273</t>
+          <t>70768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>66768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>100028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130860</t>
+          <t>129776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163065</t>
+          <t>163901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212624</t>
+          <t>211798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207922</t>
+          <t>205343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256574</t>
+          <t>255758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385146</t>
+          <t>386861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>456163</t>
+          <t>452122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118944</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>110913</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>126611</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>108670</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>101301</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>115693</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>100848</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>115322</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>118944</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>110858</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>127063</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215379</t>
+          <t>216125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237591</t>
+          <t>237917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32776</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25109</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40807</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28065</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21042</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35434</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21413</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35887</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32776</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24657</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40862</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50864</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73076</t>
+          <t>72330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>151720</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>151720</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>151720</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136735</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136735</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136735</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>151720</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>151720</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>151720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,74 +1066,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>164884</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154748</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>174139</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>150293</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>140867</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>158328</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>140507</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>158322</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>81,4%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>164884</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154669</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>173590</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>77,98%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>82,09%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>491</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301144</t>
+          <t>300733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328619</t>
+          <t>328373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46572</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37317</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56708</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44216</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36181</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36187</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>54002</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>18,6%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>46572</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>37866</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>56787</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77346</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104821</t>
+          <t>105232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>194509</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>211456</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>211456</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>211456</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>107097</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98369</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>115406</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>90777</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82304</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98946</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>82738</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98974</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>66,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>107097</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98077</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>115510</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185304</t>
+          <t>186084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210021</t>
+          <t>210284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42077</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33768</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50805</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46130</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37961</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54603</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37933</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54169</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>42077</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33664</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51097</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76060</t>
+          <t>75797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100777</t>
+          <t>99997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136907</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136907</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136907</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141443</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>130160</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>152197</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>147432</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>135697</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>158117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>136687</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>157802</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>141443</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>130431</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>151904</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274114</t>
+          <t>274009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303306</t>
+          <t>303502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65686</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54932</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76969</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59558</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48873</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49188</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65686</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>55225</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>76698</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>110617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140005</t>
+          <t>140110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206990</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206990</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206990</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>513235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>551237</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>478826</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>515681</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>480522</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>515664</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>76,38%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>532368</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>513998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>550329</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>71,44%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>76,49%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1535</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1002908</t>
+          <t>1003723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1055340</t>
+          <t>1057093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>187111</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>168242</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>206244</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>177969</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159460</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>196315</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>159477</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>194619</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>187111</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>169150</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>205481</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339280</t>
+          <t>337527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391712</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>675141</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>110222</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100092</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>118888</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>107177</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98760</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>115276</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97772</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>115158</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>110222</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>100925</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>119556</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205021</t>
+          <t>204369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228928</t>
+          <t>230486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43794</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35128</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53924</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32180</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24081</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40597</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24199</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41585</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43794</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34460</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>53091</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88352</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154016</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154016</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154016</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154016</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154016</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>159574</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>147642</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>169932</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>150691</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>140100</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>159911</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>140759</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>160229</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>159574</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>147539</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>169409</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295464</t>
+          <t>295546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324177</t>
+          <t>324617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53235</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75525</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>55667</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46447</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66258</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46129</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>65599</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>26,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63593</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53758</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>75628</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105348</t>
+          <t>104908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134061</t>
+          <t>133979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223167</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223167</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223167</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223167</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223167</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120089</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>109969</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>128609</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>102626</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>94535</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112535</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92792</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>111223</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>66,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>120089</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>110383</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128908</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208748</t>
+          <t>210135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234647</t>
+          <t>234863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37983</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56623</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>52075</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42166</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60166</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>43478</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61909</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>46503</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>37684</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>56209</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86646</t>
+          <t>86430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112545</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154701</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154701</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154701</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>148069</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>136477</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>158396</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>150457</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>138212</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>161041</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139040</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>161653</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>148069</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>136521</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>158336</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282231</t>
+          <t>282344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312740</t>
+          <t>315155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60327</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71919</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59056</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48472</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71301</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47860</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70473</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>60327</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>50060</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>71875</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105169</t>
+          <t>102754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135678</t>
+          <t>135565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>516946</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>557406</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>491483</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>531483</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>490900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>528676</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>537955</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>516931</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>557348</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019954</t>
+          <t>1019157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1078025</t>
+          <t>1074094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>214216</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>194765</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>235225</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>198978</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>178446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>218446</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>181253</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>219029</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>214216</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>194823</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>235240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384075</t>
+          <t>388006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>442146</t>
+          <t>442943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752171</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709929</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>105031</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94558</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>113699</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>106802</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98601</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114221</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>98686</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>113894</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>105031</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96250</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114155</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198590</t>
+          <t>199123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222992</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43045</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34377</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53518</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26905</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19486</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35106</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19813</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35021</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43045</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33921</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51826</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58791</t>
+          <t>58291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144842</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>132242</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>155451</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>132710</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>121697</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>143436</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>121304</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>142733</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>59,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144842</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>132883</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>155643</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,74%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260957</t>
+          <t>260853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293822</t>
+          <t>292481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78891</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68282</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91491</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73437</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62711</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84450</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63414</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>84843</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>78891</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68090</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90850</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136058</t>
+          <t>137399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168923</t>
+          <t>169027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223733</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223733</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223733</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206147</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206147</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206147</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223733</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223733</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108402</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98051</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>117568</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>102938</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>93412</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110926</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92844</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>110911</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108402</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98594</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>118485</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197184</t>
+          <t>197052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225080</t>
+          <t>224429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55975</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46809</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66326</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>50454</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42466</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59980</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>42481</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>60548</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55975</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45892</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65783</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92689</t>
+          <t>93340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120585</t>
+          <t>120717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>153392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>153392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>153392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>164377</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>164377</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>164377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>136001</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>124865</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>146939</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>138144</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>126247</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>148862</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>126094</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>149565</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>136001</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>123503</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>146603</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>67,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258075</t>
+          <t>257011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289525</t>
+          <t>289459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66055</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55117</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77191</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>67863</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57145</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>79760</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>56442</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>79913</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>66055</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>55453</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78553</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118538</t>
+          <t>118604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149988</t>
+          <t>151052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202056</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202056</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202056</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202056</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202056</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202056</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>473777</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>515717</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>716</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>458336</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>497620</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>461458</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>500683</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>472693</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>515355</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>945678</t>
+          <t>945109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1002204</t>
+          <t>1001563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>243966</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222525</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>264465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>218659</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>201633</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>240917</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>198570</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>237795</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>243966</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>222887</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>265549</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>435932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491817</t>
+          <t>492386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699253</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90228</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80741</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>98941</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>82276</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>75336</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89582</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>99299</t>
+          <t>86551</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110209</t>
+          <t>93803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>181576</t>
+          <t>176779</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168474</t>
+          <t>164786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195201</t>
+          <t>190071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34072</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43559</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32922</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25616</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39862</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72434</t>
+          <t>66874</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>53582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>78867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124300</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124300</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124300</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115198</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115198</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115198</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>119353</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>119353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>119353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>254010</t>
+          <t>243653</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254010</t>
+          <t>243653</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254010</t>
+          <t>243653</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>173724</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>160050</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>185721</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>139833</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>128491</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>149487</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>182355</t>
+          <t>135402</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168907</t>
+          <t>125204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193958</t>
+          <t>144135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>322189</t>
+          <t>309126</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305051</t>
+          <t>293710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337754</t>
+          <t>323151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63482</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51485</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>50679</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41025</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62021</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72680</t>
+          <t>49011</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61077</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86128</t>
+          <t>59209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>123359</t>
+          <t>112493</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107794</t>
+          <t>98468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140497</t>
+          <t>127909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>112567</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100332</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>124312</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>140656</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>125472</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122336</t>
+          <t>111170</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108542</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134291</t>
+          <t>119308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>262992</t>
+          <t>223737</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243568</t>
+          <t>205806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289660</t>
+          <t>237345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55475</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43730</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67710</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>47136</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29584</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>62320</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50599</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76348</t>
+          <t>52902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>109690</t>
+          <t>98741</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83022</t>
+          <t>85133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129114</t>
+          <t>116672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168042</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168042</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168042</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187792</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187792</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184890</t>
+          <t>154436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184890</t>
+          <t>154436</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184890</t>
+          <t>154436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>372682</t>
+          <t>322478</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372682</t>
+          <t>322478</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>372682</t>
+          <t>322478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>119511</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>108459</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>129431</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>106720</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>95388</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>116921</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>70,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126382</t>
+          <t>109611</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114470</t>
+          <t>99551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135842</t>
+          <t>119865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>233103</t>
+          <t>229122</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217619</t>
+          <t>214723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247367</t>
+          <t>242758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49865</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39945</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>60917</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59436</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49235</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70768</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54856</t>
+          <t>55580</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>45326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66768</t>
+          <t>65640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>114292</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100028</t>
+          <t>91809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129776</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166156</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166156</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166156</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165191</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>165191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>334567</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>334567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347395</t>
+          <t>334567</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>473783</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>630</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>447861</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>495758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442733</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>504217</t>
+          <t>424474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554632</t>
+          <t>460390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>967512</t>
+          <t>904712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1032773</t>
+          <t>966284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>180045</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>225142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>190173</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>163901</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>211798</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>229602</t>
+          <t>180659</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205343</t>
+          <t>163002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255758</t>
+          <t>198918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>419775</t>
+          <t>383552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386861</t>
+          <t>356033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>452122</t>
+          <t>417605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>659659</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>623392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1419634</t>
+          <t>1322317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
